--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>Administrator, Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr, Administrator</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -589,49 +589,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>18/28</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -807,7 +803,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -862,7 +858,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -973,7 +969,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1026,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -1335,22 +1331,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1413,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -1499,22 +1495,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -1577,22 +1573,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1655,22 +1651,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -1733,17 +1729,17 @@
         <v>20</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -1811,22 +1807,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>83.0%</t>
         </is>
       </c>
     </row>
@@ -1889,69 +1885,65 @@
         <v>20</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>85.9%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>16/31</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1971,22 +1963,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -2053,22 +2045,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2127,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -2217,22 +2209,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -3459,49 +3451,45 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>7/18</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -4444,49 +4432,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>18/21</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5399,49 +5383,45 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>29/31</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6319,49 +6299,45 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>24/28</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7239,49 +7215,45 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>26/29</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8159,49 +8131,45 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G146" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>29/33</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9079,49 +9047,45 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9999,49 +9963,45 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E186" s="4" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr">
-        <is>
-          <t>12/27</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10954,49 +10914,45 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E207" s="4" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="inlineStr">
-        <is>
-          <t>15/29</t>
-        </is>
-      </c>
-      <c r="I207" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11909,49 +11865,45 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D228" s="4" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E228" s="4" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>08/12/2025</t>
         </is>
       </c>
-      <c r="F228" s="4" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G228" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H228" s="4" t="inlineStr">
-        <is>
-          <t>12/29</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -969,7 +969,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -1269,49 +1269,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>22/28</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1331,22 +1327,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1409,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -1495,22 +1491,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -1573,22 +1569,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.1%</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1647,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -1729,22 +1725,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -1807,22 +1803,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -1885,22 +1881,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -1963,22 +1959,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -2045,22 +2041,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>79.1%</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2123,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2205,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -2955,49 +2951,45 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>23/31</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -4076,49 +4068,45 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5027,49 +5015,45 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>17/21</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5943,49 +5927,45 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>23/31</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6859,49 +6839,45 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>26/28</t>
-        </is>
-      </c>
-      <c r="I118" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7775,49 +7751,45 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>27/29</t>
-        </is>
-      </c>
-      <c r="I138" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8691,49 +8663,45 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C158" s="4" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F158" s="4" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>28/33</t>
-        </is>
-      </c>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9607,49 +9575,45 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F178" s="4" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>28/30</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10558,49 +10522,45 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F199" s="4" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H199" s="4" t="inlineStr">
-        <is>
-          <t>16/27</t>
-        </is>
-      </c>
-      <c r="I199" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11509,49 +11469,45 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C220" s="4" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D220" s="4" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E220" s="4" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F220" s="4" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G220" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H220" s="4" t="inlineStr">
-        <is>
-          <t>18/29</t>
-        </is>
-      </c>
-      <c r="I220" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12460,49 +12416,45 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C241" s="4" t="inlineStr">
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D241" s="4" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E241" s="4" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>13/12/2025</t>
         </is>
       </c>
-      <c r="F241" s="4" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G241" s="4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H241" s="4" t="inlineStr">
-        <is>
-          <t>18/29</t>
-        </is>
-      </c>
-      <c r="I241" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +965,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -1405,22 +1405,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1487,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -1565,22 +1565,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -1975,49 +1975,45 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>26/31</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2037,22 +2033,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -2119,22 +2115,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2197,17 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P26" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
@@ -3497,49 +3493,45 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>14/18</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -4459,49 +4451,45 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>14/21</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9946,49 +9934,45 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H187" s="5" t="inlineStr">
-        <is>
-          <t>17/27</t>
-        </is>
-      </c>
-      <c r="I187" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10893,49 +10877,45 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B208" s="5" t="inlineStr">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D208" s="5" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E208" s="5" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H208" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I208" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11840,49 +11820,45 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B229" s="5" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C229" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D229" s="5" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E229" s="5" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>16/12/2025</t>
         </is>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I229" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +965,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -1405,22 +1405,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>74.9%</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1487,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1565,22 +1565,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -2033,17 +2033,17 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -2053,49 +2053,45 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>24/31</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2115,22 +2111,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -2197,22 +2193,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
     </row>
@@ -3551,49 +3547,45 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>11/18</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4494,49 +4486,45 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>20/21</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9977,49 +9965,45 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H188" s="5" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="I188" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10920,49 +10904,45 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E209" s="5" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H209" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I209" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11863,49 +11843,45 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B230" s="5" t="inlineStr">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C230" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D230" s="5" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E230" s="5" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>17/12/2025</t>
         </is>
       </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G230" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H230" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I230" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -693,49 +693,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>24/28</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -799,7 +795,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +850,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +961,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -1323,22 +1319,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1639,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>80.1%</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1717,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -1799,22 +1795,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -1877,22 +1873,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>84.3%</t>
         </is>
       </c>
     </row>
@@ -1955,22 +1951,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -5425,49 +5421,45 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>30/31</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6333,49 +6325,45 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>27/28</t>
-        </is>
-      </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7241,49 +7229,45 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>29/29</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8149,49 +8133,45 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E148" s="5" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>32/33</t>
-        </is>
-      </c>
-      <c r="I148" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9057,49 +9037,45 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B168" s="5" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E168" s="5" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>21/12/2025</t>
         </is>
       </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I168" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -744,49 +744,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>19/28</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -795,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -850,7 +846,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -961,7 +957,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -1319,22 +1315,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -1639,22 +1635,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1717,22 +1713,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -1795,22 +1791,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1869,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -1951,22 +1947,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.0%</t>
         </is>
       </c>
     </row>
@@ -5464,49 +5460,45 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>25/31</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6368,49 +6360,45 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>24/28</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7272,49 +7260,45 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>27/29</t>
-        </is>
-      </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8176,49 +8160,45 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr">
-        <is>
-          <t>30/33</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9080,49 +9060,45 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>22/12/2025</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G169" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr">
-        <is>
-          <t>21/30</t>
-        </is>
-      </c>
-      <c r="I169" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +957,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>41.9%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1397,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1479,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -2025,22 +2025,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -2103,69 +2103,65 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>29/31</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2185,22 +2181,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -3582,49 +3578,45 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>13/18</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4521,49 +4513,45 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>17/21</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9960,49 +9948,45 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="I189" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10899,49 +10883,45 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H210" s="5" t="inlineStr">
-        <is>
-          <t>28/29</t>
-        </is>
-      </c>
-      <c r="I210" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11838,49 +11818,45 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B231" s="5" t="inlineStr">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D231" s="5" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E231" s="5" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>23/12/2025</t>
         </is>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="inlineStr">
-        <is>
-          <t>29/29</t>
-        </is>
-      </c>
-      <c r="I231" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +957,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1397,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.8%</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1479,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -2025,22 +2025,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -2103,22 +2103,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -2181,69 +2181,65 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>22/31</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -3621,49 +3617,45 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>12/18</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4556,49 +4548,45 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>19/21</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9991,49 +9979,45 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H190" s="5" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="I190" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10926,49 +10910,45 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="5" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E211" s="5" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H211" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I211" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11861,49 +11841,45 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B232" s="5" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D232" s="5" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E232" s="5" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H232" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I232" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +957,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>30.2%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -1315,69 +1315,65 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>22/28</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1397,69 +1393,65 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>22/28</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1479,22 +1471,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>82.2%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1549,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
@@ -1635,22 +1627,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.8%</t>
         </is>
       </c>
     </row>
@@ -1713,22 +1705,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -1791,22 +1783,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -1869,22 +1861,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1947,22 +1939,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -2025,22 +2017,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -2103,22 +2095,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -2181,22 +2173,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -3001,49 +2993,45 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>18/31</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -3083,49 +3071,45 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>18/31</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -4067,96 +4051,88 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>12/18</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>12/18</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4998,96 +4974,88 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>18/21</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>18/21</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5898,96 +5866,88 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>25/31</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>25/31</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6798,96 +6758,88 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>25/28</t>
-        </is>
-      </c>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>25/28</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7698,96 +7650,88 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8598,96 +8542,88 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G159" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr">
-        <is>
-          <t>28/33</t>
-        </is>
-      </c>
-      <c r="I159" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E160" s="5" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F160" s="5" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G160" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H160" s="5" t="inlineStr">
-        <is>
-          <t>28/33</t>
-        </is>
-      </c>
-      <c r="I160" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9498,96 +9434,88 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E179" s="5" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F179" s="5" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G179" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H179" s="5" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C180" s="5" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E180" s="5" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H180" s="5" t="inlineStr">
-        <is>
-          <t>24/30</t>
-        </is>
-      </c>
-      <c r="I180" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10429,96 +10357,88 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B200" s="5" t="inlineStr">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C200" s="5" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D200" s="5" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E200" s="5" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F200" s="5" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G200" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H200" s="5" t="inlineStr">
-        <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="I200" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C201" s="5" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D201" s="5" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E201" s="5" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F201" s="5" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H201" s="5" t="inlineStr">
-        <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="I201" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11360,96 +11280,88 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B221" s="5" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C221" s="5" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D221" s="5" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E221" s="5" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F221" s="5" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G221" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I221" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B222" s="5" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C222" s="5" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D222" s="5" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E222" s="5" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F222" s="5" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G222" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H222" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I222" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12291,96 +12203,88 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G242" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H242" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I242" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
+      <c r="C243" s="2" t="inlineStr">
         <is>
           <t>SURGERY SEMINAR/SLIDE</t>
         </is>
       </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>27/12/2025</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G243" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H243" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,53 +791,49 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>26/28</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -846,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +953,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1010,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -1315,22 +1311,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -1627,22 +1623,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1701,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1783,22 +1779,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -1861,22 +1857,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -1939,17 +1935,17 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -5447,49 +5443,45 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>28/31</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6339,49 +6331,45 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="inlineStr">
-        <is>
-          <t>28/28</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7231,49 +7219,45 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8123,49 +8107,45 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H150" s="5" t="inlineStr">
-        <is>
-          <t>32/33</t>
-        </is>
-      </c>
-      <c r="I150" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9015,49 +8995,45 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B170" s="5" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C170" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E170" s="5" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>28/12/2025</t>
         </is>
       </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G170" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H170" s="5" t="inlineStr">
-        <is>
-          <t>25/30</t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -842,53 +842,49 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>25/28</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -953,7 +949,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>25.6%</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1006,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>78.5%</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1307,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -1623,22 +1619,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -1701,22 +1697,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -1779,22 +1775,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
@@ -1857,22 +1853,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -1935,22 +1931,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>82.8%</t>
         </is>
       </c>
     </row>
@@ -5486,49 +5482,45 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>28/31</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6374,49 +6366,45 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>28/28</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7262,49 +7250,45 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>29/29</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8150,49 +8134,45 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr">
-        <is>
-          <t>33/33</t>
-        </is>
-      </c>
-      <c r="I151" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9038,49 +9018,45 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E171" s="5" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>29/12/2025</t>
         </is>
       </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>27/30</t>
-        </is>
-      </c>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -949,7 +949,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -1385,22 +1385,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -1463,22 +1463,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>84.7%</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -2087,22 +2087,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2165,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>84.5%</t>
         </is>
       </c>
     </row>
@@ -2263,49 +2263,45 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>27/31</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -3636,49 +3632,45 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>13/18</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4559,49 +4551,45 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>15/21</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9902,49 +9890,45 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E191" s="5" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H191" s="5" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="I191" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10825,49 +10809,45 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H212" s="5" t="inlineStr">
-        <is>
-          <t>21/29</t>
-        </is>
-      </c>
-      <c r="I212" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11748,49 +11728,45 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>30/12/2025</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="inlineStr">
-        <is>
-          <t>19/29</t>
-        </is>
-      </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
@@ -949,7 +949,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -1385,22 +1385,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -1463,22 +1463,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>87.0%</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -2009,22 +2009,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -2087,22 +2087,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2165,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -2341,49 +2341,45 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>24/31</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -3675,49 +3671,45 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>14/18</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4594,49 +4586,45 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>17/21</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9933,49 +9921,45 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B192" s="5" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C192" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E192" s="5" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H192" s="5" t="inlineStr">
-        <is>
-          <t>18/27</t>
-        </is>
-      </c>
-      <c r="I192" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10852,49 +10836,45 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11771,49 +11751,45 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E234" s="5" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>31/12/2025</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H234" s="5" t="inlineStr">
-        <is>
-          <t>27/29</t>
-        </is>
-      </c>
-      <c r="I234" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8">
@@ -897,49 +897,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>25/28</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -949,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1002,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>77.9%</t>
         </is>
       </c>
     </row>
@@ -1307,22 +1303,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1615,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>72.9%</t>
         </is>
       </c>
     </row>
@@ -1697,22 +1693,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1771,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -1853,22 +1849,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>77.0%</t>
         </is>
       </c>
     </row>
@@ -1931,22 +1927,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>82.0%</t>
         </is>
       </c>
     </row>
@@ -5501,49 +5497,45 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>29/31</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6385,49 +6377,45 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H112" s="5" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7269,49 +7257,45 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I132" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8153,49 +8137,45 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>28/33</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9037,49 +9017,45 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B172" s="5" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E172" s="5" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>04/01/2026</t>
         </is>
       </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G172" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H172" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I172" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -945,54 +945,50 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>24/28</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1002,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -1303,22 +1299,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1615,22 +1611,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>66.9%</t>
         </is>
       </c>
     </row>
@@ -1693,22 +1689,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -1771,22 +1767,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -1849,22 +1845,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>73.5%</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1923,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -5540,49 +5536,45 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>30/31</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6420,49 +6412,45 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>25/28</t>
-        </is>
-      </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7300,49 +7288,45 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr">
-        <is>
-          <t>28/29</t>
-        </is>
-      </c>
-      <c r="I133" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8180,49 +8164,45 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E153" s="5" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>30/33</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9060,49 +9040,45 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E173" s="5" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G173" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="inlineStr">
-        <is>
-          <t>29/30</t>
-        </is>
-      </c>
-      <c r="I173" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -1377,22 +1377,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -2001,22 +2001,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -2079,22 +2079,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -2157,22 +2157,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -2567,49 +2567,45 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>26/31</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -3792,49 +3788,45 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>17/18</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4707,49 +4699,45 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>20/21</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10002,49 +9990,45 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C195" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D195" s="5" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E195" s="5" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H195" s="5" t="inlineStr">
-        <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="I195" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10917,49 +10901,45 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H216" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I216" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11832,49 +11812,45 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>11/01/2026</t>
         </is>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H237" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -1377,22 +1377,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1455,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -2001,17 +2001,17 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -2079,22 +2079,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -2157,22 +2157,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -2645,49 +2645,45 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>27/31</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -3831,49 +3827,45 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>16/18</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4742,49 +4734,45 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>16/21</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10033,49 +10021,45 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E196" s="5" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H196" s="5" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="I196" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10944,49 +10928,45 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H217" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I217" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11855,49 +11835,45 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H238" s="5" t="inlineStr">
-        <is>
-          <t>25/29</t>
-        </is>
-      </c>
-      <c r="I238" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -998,54 +998,50 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>26/28</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1299,22 +1295,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -1611,22 +1607,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -1689,22 +1685,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -1767,22 +1763,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1845,22 +1841,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
     </row>
@@ -1923,22 +1919,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -5555,49 +5551,45 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>31/31</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6431,49 +6423,45 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>27/28</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7307,49 +7295,45 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>28/29</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8183,49 +8167,45 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E154" s="5" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H154" s="5" t="inlineStr">
-        <is>
-          <t>33/33</t>
-        </is>
-      </c>
-      <c r="I154" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9059,49 +9039,45 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E174" s="5" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>13/01/2026</t>
         </is>
       </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G174" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H174" s="5" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="I174" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -1046,49 +1046,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>19/28</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1295,22 +1291,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -1607,22 +1603,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1681,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -1763,22 +1759,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1837,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>57.6%</t>
         </is>
       </c>
     </row>
@@ -1919,22 +1915,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -5594,49 +5590,45 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>17/31</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6466,49 +6458,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I115" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7338,49 +7326,45 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E135" s="5" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>15/29</t>
-        </is>
-      </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8210,49 +8194,45 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="inlineStr">
-        <is>
-          <t>26/33</t>
-        </is>
-      </c>
-      <c r="I155" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9082,49 +9062,45 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E175" s="5" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>26/30</t>
-        </is>
-      </c>
-      <c r="I175" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1369,22 @@
         <v>21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1447,22 @@
         <v>21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1525,22 +1525,22 @@
         <v>21</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1993,22 +1993,22 @@
         <v>21</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2071,22 +2071,22 @@
         <v>21</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2149,22 +2149,22 @@
         <v>21</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2715,49 +2715,45 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>B1-10</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>18/01/2026</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>18/31</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -3862,49 +3858,45 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>B1-11</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>18/01/2026</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>14/18</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0/18</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4769,49 +4761,45 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>B1-12</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>18/01/2026</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>11/21</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0/21</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10016,49 +10004,45 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B197" s="5" t="inlineStr">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>B1-7</t>
         </is>
       </c>
-      <c r="C197" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D197" s="5" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E197" s="5" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>18/01/2026</t>
         </is>
       </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H197" s="5" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="I197" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>0/27</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10923,49 +10907,45 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B218" s="5" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>B1-8</t>
         </is>
       </c>
-      <c r="C218" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D218" s="5" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E218" s="5" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>18/01/2026</t>
         </is>
       </c>
-      <c r="F218" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G218" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H218" s="5" t="inlineStr">
-        <is>
-          <t>23/29</t>
-        </is>
-      </c>
-      <c r="I218" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11830,49 +11810,45 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>B1-9</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>18/01/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="inlineStr">
-        <is>
-          <t>22/29</t>
-        </is>
-      </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +945,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -1089,49 +1089,45 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>23/28</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1291,22 +1287,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1599,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -1681,22 +1677,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1755,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -1837,22 +1833,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -1915,17 +1911,17 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -5621,49 +5617,45 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>21/31</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6489,49 +6481,45 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>18/28</t>
-        </is>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7357,49 +7345,45 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>24/29</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8225,49 +8209,45 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B156" s="5" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C156" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E156" s="5" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H156" s="5" t="inlineStr">
-        <is>
-          <t>22/33</t>
-        </is>
-      </c>
-      <c r="I156" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9093,49 +9073,45 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>19/30</t>
-        </is>
-      </c>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Surgery_2_B1_session_analysis.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -91,9 +91,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -791,7 +788,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -842,7 +839,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8">
@@ -945,7 +942,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -998,7 +995,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1137,49 +1134,45 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>B1-1</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>16/28</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1287,22 +1280,22 @@
         <v>20</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1599,22 +1592,22 @@
         <v>20</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1677,22 +1670,22 @@
         <v>20</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1755,22 +1748,22 @@
         <v>20</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1833,22 +1826,22 @@
         <v>20</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1911,22 +1904,22 @@
         <v>20</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3332,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -3397,7 +3390,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -3455,7 +3448,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -5660,49 +5653,45 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>B1-2</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>14/31</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6524,49 +6513,45 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>B1-3</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr">
-        <is>
-          <t>8/28</t>
-        </is>
-      </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7388,49 +7373,45 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>B1-4</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr">
-        <is>
-          <t>19/29</t>
-        </is>
-      </c>
-      <c r="I137" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8252,49 +8233,45 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>B1-5</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr">
-        <is>
-          <t>16/33</t>
-        </is>
-      </c>
-      <c r="I157" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>0/33</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9116,49 +9093,45 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>B1-6</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E177" s="5" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="G177" s="5" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>19/30</t>
-        </is>
-      </c>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>Recorded</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
